--- a/Sprint 1/sprint_backlog/Sprint backlog card 16.xlsx
+++ b/Sprint 1/sprint_backlog/Sprint backlog card 16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ปี 3\PaiNamNaeWebApp\Sprint 1\sprint_backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D8027D5-AD91-4CAC-8B93-4D4597172220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50928CC5-1EFE-4FFB-9115-F8BFB7710310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{95F319A4-3021-4B35-9753-B79CED767C2B}"/>
   </bookViews>
